--- a/docs/downloads/08/tbl_produits_elevage_alaotra_avaradrano.xlsx
+++ b/docs/downloads/08/tbl_produits_elevage_alaotra_avaradrano.xlsx
@@ -427,9 +427,6 @@
           <t>Vorona</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -487,9 +484,6 @@
           <t>Henan'ondry</t>
         </is>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -502,9 +496,6 @@
           <t>Henan-Kisoa</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -531,9 +522,6 @@
         <is>
           <t>Vorona</t>
         </is>
-      </c>
-      <c r="C12">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
